--- a/Result/profitability/1440.xlsx
+++ b/Result/profitability/1440.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04750000000000002</v>
+        <v>-0.02125000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>7.03125</v>
+        <v>8.185</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03250000000000001</v>
+        <v>0.01499999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>8.0275</v>
+        <v>9.295</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002499999999999985</v>
+        <v>0.03124999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.715</v>
+        <v>9.505000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.01750000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>6.7075</v>
+        <v>7.241250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03500000000000002</v>
+        <v>-0.01250000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>6.58</v>
+        <v>7.3275</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.008750000000000015</v>
+        <v>0.02749999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>7.47625</v>
+        <v>8.147499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02374999999999999</v>
+        <v>0.05249999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>8.19</v>
+        <v>8.70125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06124999999999999</v>
+        <v>0.06124999999999998</v>
       </c>
       <c r="N9" t="n">
         <v>8.96875</v>
@@ -9830,6 +9830,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3191</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2782</v>
+      </c>
+      <c r="E75" t="n">
+        <v>409</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>302</v>
+      </c>
+      <c r="J75" t="n">
+        <v>321</v>
+      </c>
+      <c r="K75" t="n">
+        <v>304</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03250000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.145</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4684994272623138</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4994152046783624</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
